--- a/Assets/ArtRes/Excel/游戏机制配置表.xlsx
+++ b/Assets/ArtRes/Excel/游戏机制配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13070" windowHeight="4410"/>
+    <workbookView windowWidth="13070" windowHeight="4420"/>
   </bookViews>
   <sheets>
     <sheet name="IteratValueInfo" sheetId="1" r:id="rId1"/>
@@ -1056,7 +1056,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>0</v>
